--- a/data/library_info/Broad Compound Registration Melis to date.xlsx
+++ b/data/library_info/Broad Compound Registration Melis to date.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10312"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10215"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/melisanahtar/Dropbox (Personal)/Collins Lab/Neisseria gonorrhoeae/Externally ordered compounds/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jackie16201/Desktop/Spring_2023/ngonorrhoeae_abx_ml_discovery/data/library_info/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C1842EE-258B-5646-A2B8-8CFF3C2B485C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9943DB0C-890E-164B-82EA-8983AFD7DAE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1280" yWindow="880" windowWidth="30240" windowHeight="17220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="26240" windowHeight="16360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
@@ -43,46 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="612">
-  <si>
-    <t>Stereo Comments</t>
-  </si>
-  <si>
-    <t>Alternate Name</t>
-  </si>
-  <si>
-    <t>Notebook ID</t>
-  </si>
-  <si>
-    <t>Page ID</t>
-  </si>
-  <si>
-    <t>Supplier</t>
-  </si>
-  <si>
-    <t>Supplier Catalog</t>
-  </si>
-  <si>
-    <t>Comments</t>
-  </si>
-  <si>
-    <t>Barcode</t>
-  </si>
-  <si>
-    <t>Amount</t>
-  </si>
-  <si>
-    <t>Units</t>
-  </si>
-  <si>
-    <t>Concentration</t>
-  </si>
-  <si>
-    <t>Concentration Units</t>
-  </si>
-  <si>
-    <t>Solvent</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="458">
   <si>
     <t>as drawn</t>
   </si>
@@ -1188,102 +1148,6 @@
     <t>SMILES</t>
   </si>
   <si>
-    <t>Project Code</t>
-  </si>
-  <si>
-    <t>Broad Username</t>
-  </si>
-  <si>
-    <t>Well</t>
-  </si>
-  <si>
-    <t>Plate Format</t>
-  </si>
-  <si>
-    <t>TV173245</t>
-  </si>
-  <si>
-    <t>TV173246</t>
-  </si>
-  <si>
-    <t>TV173247</t>
-  </si>
-  <si>
-    <t>TV173248</t>
-  </si>
-  <si>
-    <t>TV173249</t>
-  </si>
-  <si>
-    <t>TV173250</t>
-  </si>
-  <si>
-    <t>TV173251</t>
-  </si>
-  <si>
-    <t>TV173252</t>
-  </si>
-  <si>
-    <t>TV173253</t>
-  </si>
-  <si>
-    <t>TV173254</t>
-  </si>
-  <si>
-    <t>TV173255</t>
-  </si>
-  <si>
-    <t>TV173256</t>
-  </si>
-  <si>
-    <t>TV173257</t>
-  </si>
-  <si>
-    <t>TV173258</t>
-  </si>
-  <si>
-    <t>TV173259</t>
-  </si>
-  <si>
-    <t>TV173260</t>
-  </si>
-  <si>
-    <t>TV173261</t>
-  </si>
-  <si>
-    <t>TV173262</t>
-  </si>
-  <si>
-    <t>TV173263</t>
-  </si>
-  <si>
-    <t>TV173264</t>
-  </si>
-  <si>
-    <t>TV173265</t>
-  </si>
-  <si>
-    <t>TV173266</t>
-  </si>
-  <si>
-    <t>TV173267</t>
-  </si>
-  <si>
-    <t>TV173655</t>
-  </si>
-  <si>
-    <t>TV173656</t>
-  </si>
-  <si>
-    <t>TV173657</t>
-  </si>
-  <si>
-    <t>TV173658</t>
-  </si>
-  <si>
-    <t>TV173659</t>
-  </si>
-  <si>
     <t>[O-][N+](=O)C1=CC=C(O1)C(=O)NC1=C(C=CC=C1)[N+]([O-])=O</t>
   </si>
   <si>
@@ -1368,186 +1232,6 @@
     <t>CCOC(=O)C1=CSC(NC(=O)C2=CC=C(O2)[N+]([O-])=O)=N1</t>
   </si>
   <si>
-    <t>achiral</t>
-  </si>
-  <si>
-    <t>chiral</t>
-  </si>
-  <si>
-    <t>STK390491</t>
-  </si>
-  <si>
-    <t>STK095259</t>
-  </si>
-  <si>
-    <t>STK697705</t>
-  </si>
-  <si>
-    <t>STK043403</t>
-  </si>
-  <si>
-    <t>STK551123</t>
-  </si>
-  <si>
-    <t>STK615539</t>
-  </si>
-  <si>
-    <t>STK697903</t>
-  </si>
-  <si>
-    <t>STK874126</t>
-  </si>
-  <si>
-    <t>STK328950</t>
-  </si>
-  <si>
-    <t>STK344349</t>
-  </si>
-  <si>
-    <t>STK081484</t>
-  </si>
-  <si>
-    <t>STK851771</t>
-  </si>
-  <si>
-    <t>STK005412</t>
-  </si>
-  <si>
-    <t>STL041447</t>
-  </si>
-  <si>
-    <t>STL055322</t>
-  </si>
-  <si>
-    <t>STL041955</t>
-  </si>
-  <si>
-    <t>STL260990</t>
-  </si>
-  <si>
-    <t>STL112736</t>
-  </si>
-  <si>
-    <t>ST105244</t>
-  </si>
-  <si>
-    <t>HTS11128</t>
-  </si>
-  <si>
-    <t>S13239</t>
-  </si>
-  <si>
-    <t>BR00068</t>
-  </si>
-  <si>
-    <t>S08178</t>
-  </si>
-  <si>
-    <t>Menai</t>
-  </si>
-  <si>
-    <t>ES58</t>
-  </si>
-  <si>
-    <t>99589754</t>
-  </si>
-  <si>
-    <t>29229678</t>
-  </si>
-  <si>
-    <t>5331967</t>
-  </si>
-  <si>
-    <t>5957206</t>
-  </si>
-  <si>
-    <t>manahtar</t>
-  </si>
-  <si>
-    <t>MP1</t>
-  </si>
-  <si>
-    <t>MP3</t>
-  </si>
-  <si>
-    <t>MP4</t>
-  </si>
-  <si>
-    <t>MP5</t>
-  </si>
-  <si>
-    <t>MP6</t>
-  </si>
-  <si>
-    <t>MP7</t>
-  </si>
-  <si>
-    <t>MP9</t>
-  </si>
-  <si>
-    <t>MP11</t>
-  </si>
-  <si>
-    <t>MP13</t>
-  </si>
-  <si>
-    <t>MP14</t>
-  </si>
-  <si>
-    <t>MP15</t>
-  </si>
-  <si>
-    <t>MP16</t>
-  </si>
-  <si>
-    <t>MP18</t>
-  </si>
-  <si>
-    <t>MP20</t>
-  </si>
-  <si>
-    <t>MP21</t>
-  </si>
-  <si>
-    <t>MP22</t>
-  </si>
-  <si>
-    <t>MP29</t>
-  </si>
-  <si>
-    <t>MP32</t>
-  </si>
-  <si>
-    <t>MP36</t>
-  </si>
-  <si>
-    <t>MP38</t>
-  </si>
-  <si>
-    <t>MP40</t>
-  </si>
-  <si>
-    <t>MP41</t>
-  </si>
-  <si>
-    <t>MP42</t>
-  </si>
-  <si>
-    <t>MP46</t>
-  </si>
-  <si>
-    <t>MP53</t>
-  </si>
-  <si>
-    <t>MP54</t>
-  </si>
-  <si>
-    <t>MP55</t>
-  </si>
-  <si>
-    <t>MP57</t>
-  </si>
-  <si>
     <t>BRD-K00116392-001-01-9</t>
   </si>
   <si>
@@ -1641,254 +1325,104 @@
     <t>OCC1=CC(=O)[C@@H]2O[C@@H]2C1=O |t:2|</t>
   </si>
   <si>
-    <t>7312</t>
-  </si>
-  <si>
-    <t>TV173660</t>
-  </si>
-  <si>
-    <t>CFN97901</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>KROSE</t>
-  </si>
-  <si>
-    <t>MP43</t>
-  </si>
-  <si>
     <t>BRD-K76927775-001-17-9</t>
   </si>
   <si>
     <t>[O-][N+](=O)c1ccc(\C=N\N2CC(=O)NC2=O)o1</t>
   </si>
   <si>
-    <t>TV172374</t>
-  </si>
-  <si>
-    <t>PHR1191</t>
-  </si>
-  <si>
-    <t>Nitrofurantoin</t>
-  </si>
-  <si>
     <t>BRD-K74501079-001-21-9</t>
   </si>
   <si>
     <t>CC[C@H]1OC(=O)[C@H](C)[C@@H](O[C@H]2C[C@@](C)(OC)[C@@H](O)[C@H](C)O2)[C@H](C)[C@@H](O[C@@H]2O[C@H](C)C[C@@H]([C@H]2O)N(C)C)[C@](C)(O)C[C@@H](C)CN(C)[C@H](C)[C@@H](O)[C@]1(C)O</t>
   </si>
   <si>
-    <t>TV168131</t>
-  </si>
-  <si>
-    <t>75199-25MG-F</t>
-  </si>
-  <si>
-    <t>Azithromycin</t>
-  </si>
-  <si>
-    <t>sshrivas</t>
-  </si>
-  <si>
-    <t>10 mg/mL</t>
-  </si>
-  <si>
     <t>BRD-K00126774-004-01-9</t>
   </si>
   <si>
     <t>COC(=O)c1ccc(C[n+]2cc(-c3ccccc3)n3CCCc23)cc1.Br</t>
   </si>
   <si>
-    <t>TV176543</t>
-  </si>
-  <si>
-    <t>Z56774893</t>
-  </si>
-  <si>
-    <t>413.3 g/mol</t>
-  </si>
-  <si>
     <t>BRD-K00126775-003-01-9</t>
   </si>
   <si>
     <t>C(c1ccccc1)[n+]1cc(-c2ccccc2)n2CCCc12.Cl</t>
   </si>
   <si>
-    <t>TV176544</t>
-  </si>
-  <si>
-    <t>Z56776049</t>
-  </si>
-  <si>
-    <t>310.8 g/mol</t>
-  </si>
-  <si>
     <t>BRD-K00126776-001-01-9</t>
   </si>
   <si>
     <t>Cn1cc[n+]2C[C@@H](C(O)=O)[C@@](O)(c12)C(F)(F)F |&amp;1:6,&amp;2:10,r|</t>
   </si>
   <si>
-    <t>TV176545</t>
-  </si>
-  <si>
-    <t>Z314662310</t>
-  </si>
-  <si>
-    <t>250.17 gmol</t>
-  </si>
-  <si>
     <t>BRD-K00127412-004-01-9</t>
   </si>
   <si>
     <t>[O-][N+](=O)c1ccc(C[n+]2cc(-c3ccc(Cl)c(Cl)c3)n3CCCc23)cc1.Br</t>
   </si>
   <si>
-    <t>TV176541</t>
-  </si>
-  <si>
-    <t>5865514</t>
-  </si>
-  <si>
-    <t>50 mg/mL</t>
-  </si>
-  <si>
     <t>BRD-K09974254-004-07-9</t>
   </si>
   <si>
     <t>COc1ccc(cc1)-[n+]1c2CCCn2cc1-c1ccc(Br)cc1.Br</t>
   </si>
   <si>
-    <t>TV176542</t>
-  </si>
-  <si>
-    <t>5866038</t>
-  </si>
-  <si>
-    <t>25 mg/mL</t>
-  </si>
-  <si>
     <t>BRD-K00127413-004-01-9</t>
   </si>
   <si>
     <t>COc1ccc(cc1)C(=O)C[n+]1cc(-c2ccc(OC)cc2)n2CCCc12.Br</t>
   </si>
   <si>
-    <t>TV176546</t>
-  </si>
-  <si>
-    <t>5870876</t>
-  </si>
-  <si>
     <t>BRD-K00117668-004-02-9</t>
   </si>
   <si>
     <t>Clc1ccc(cc1)-c1c[n+](Cc2ccc(Cl)cc2Cl)c2CCCn12.Br</t>
   </si>
   <si>
-    <t>TV176547</t>
-  </si>
-  <si>
-    <t>F0039-0050</t>
-  </si>
-  <si>
     <t>BRD-K00126775-003-02-9</t>
   </si>
   <si>
-    <t>TV176548</t>
-  </si>
-  <si>
-    <t>ChemSpace</t>
-  </si>
-  <si>
-    <t>CSSS00000009164</t>
-  </si>
-  <si>
     <t>BRD-K10647544-001-16-9</t>
   </si>
   <si>
     <t>[O-][N+](=O)c1ccc(C=NN2CCOC2=O)o1</t>
   </si>
   <si>
-    <t>TV176549</t>
-  </si>
-  <si>
-    <t>46297</t>
-  </si>
-  <si>
-    <t>Furazolidone</t>
-  </si>
-  <si>
     <t>BRD-K66786402-003-07-9</t>
   </si>
   <si>
     <t>Cc1ccc(C[n+]2cc(-c3ccc(Cl)cc3)n3CCCc23)cc1.Cl</t>
   </si>
   <si>
-    <t>TV174240</t>
-  </si>
-  <si>
-    <t>STL049981</t>
-  </si>
-  <si>
     <t>BRD-K00127441-003-01-9</t>
   </si>
   <si>
     <t>Cc1ccccc1C[n+]1cc(-c2ccc(Cl)cc2)n2CCCc12.Cl</t>
   </si>
   <si>
-    <t>TV176552</t>
-  </si>
-  <si>
-    <t>STL048885</t>
-  </si>
-  <si>
     <t>BRD-K46287408-003-07-9</t>
   </si>
   <si>
     <t>Clc1ccc(C[n+]2cc(-c3ccc(Cl)cc3)n3CCCc23)cc1.Cl</t>
   </si>
   <si>
-    <t>TV176563</t>
-  </si>
-  <si>
-    <t>STL055460</t>
-  </si>
-  <si>
     <t>BRD-K00127442-003-01-9</t>
   </si>
   <si>
     <t>Fc1ccc(cc1)-c1c[n+](Cc2ccc(Cl)c(Cl)c2)c2CCCn12.Cl</t>
   </si>
   <si>
-    <t>TV176564</t>
-  </si>
-  <si>
-    <t>STL042648</t>
-  </si>
-  <si>
     <t>BRD-K00127443-003-01-9</t>
   </si>
   <si>
     <t>Cc1ccccc1C[n+]1cc(-c2ccc(Cl)c(Cl)c2)n2CCCc12.Cl</t>
-  </si>
-  <si>
-    <t>TV176558</t>
-  </si>
-  <si>
-    <t>STL041594</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.00_ "/>
-  </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1906,36 +1440,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -1965,39 +1480,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2279,2239 +1782,470 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S46"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
-    <col min="2" max="2" width="55.83203125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="28.1640625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="11.1640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" customWidth="1"/>
-    <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.6640625" customWidth="1"/>
-    <col min="9" max="9" width="16" customWidth="1"/>
-    <col min="10" max="11" width="16.6640625" style="4" customWidth="1"/>
-    <col min="12" max="12" width="14" style="4" customWidth="1"/>
-    <col min="13" max="13" width="10" style="4" customWidth="1"/>
-    <col min="14" max="14" width="14.6640625" customWidth="1"/>
-    <col min="15" max="15" width="18.33203125" customWidth="1"/>
-    <col min="16" max="18" width="12.5" customWidth="1"/>
-    <col min="19" max="19" width="21.6640625" customWidth="1"/>
+    <col min="2" max="2" width="55.83203125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C1" s="4"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="C2" s="5"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="C3" s="5"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="C4" s="5"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="C5" s="5"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="C6" s="5"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="C7" s="5"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="C8" s="5"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="C9" s="5"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="C10" s="5"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="C11" s="5"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="C12" s="5"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="C13" s="5"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>380</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="C14" s="5"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>381</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K1" s="3" t="s">
+      <c r="C15" s="5"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="L1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q1" s="3" t="s">
+      <c r="C16" s="5"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>383</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="C17" s="5"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>384</v>
       </c>
-      <c r="S1" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>501</v>
-      </c>
-      <c r="B2" s="10" t="s">
+      <c r="C18" s="5"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="B19" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="C19" s="5"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="C20" s="5"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="C21" s="5"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="C22" s="5"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="C23" s="5"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="C24" s="5"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="C25" s="5"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="C26" s="5"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="C27" s="5"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="C28" s="5"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="C29" s="5"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="C30" s="5"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="C31" s="5"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="C32" s="5"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="C33" s="5"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="C34" s="5"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="C35" s="5"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="C36" s="5"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="C37" s="5"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" s="7" t="s">
         <v>441</v>
       </c>
-      <c r="D2" s="4">
-        <v>7312</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>385</v>
-      </c>
-      <c r="F2" s="1">
-        <v>200</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="I2" s="11" t="s">
+      <c r="B38" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="C38" s="5"/>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" s="7" t="s">
         <v>443</v>
       </c>
-      <c r="J2" s="5" t="s">
-        <v>473</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="L2" s="5"/>
-      <c r="N2">
-        <v>10</v>
-      </c>
-      <c r="O2" t="s">
-        <v>376</v>
-      </c>
-      <c r="P2" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>502</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>414</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>441</v>
-      </c>
-      <c r="D3" s="4">
-        <v>7312</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="F3" s="7">
-        <v>250</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="I3" s="10" t="s">
+      <c r="B39" s="7" t="s">
         <v>444</v>
       </c>
-      <c r="J3" s="5" t="s">
-        <v>474</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="L3" s="1"/>
-      <c r="N3">
-        <v>10</v>
-      </c>
-      <c r="O3" t="s">
-        <v>376</v>
-      </c>
-      <c r="P3" t="s">
-        <v>379</v>
-      </c>
-      <c r="S3" s="8"/>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>415</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>441</v>
-      </c>
-      <c r="D4" s="4">
-        <v>7312</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>387</v>
-      </c>
-      <c r="F4" s="7">
-        <v>250</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="I4" s="11" t="s">
+      <c r="C39" s="5"/>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" s="7" t="s">
         <v>445</v>
       </c>
-      <c r="J4" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="L4" s="5"/>
-      <c r="N4">
-        <v>10</v>
-      </c>
-      <c r="O4" t="s">
-        <v>376</v>
-      </c>
-      <c r="P4" t="s">
-        <v>379</v>
-      </c>
-      <c r="S4" s="8"/>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>504</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>416</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>441</v>
-      </c>
-      <c r="D5" s="4">
-        <v>7312</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="F5" s="1">
-        <v>250</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="I5" s="11" t="s">
+      <c r="B40" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="C40" s="5"/>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41" s="7" t="s">
         <v>446</v>
       </c>
-      <c r="J5" s="5" t="s">
-        <v>476</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="L5" s="5"/>
-      <c r="N5">
-        <v>10</v>
-      </c>
-      <c r="O5" t="s">
-        <v>376</v>
-      </c>
-      <c r="P5" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>505</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>417</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>442</v>
-      </c>
-      <c r="D6" s="4">
-        <v>7312</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>389</v>
-      </c>
-      <c r="F6" s="1">
-        <v>250</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="I6" s="11" t="s">
+      <c r="B41" s="7" t="s">
         <v>447</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="L6" s="1"/>
-      <c r="N6">
-        <v>10</v>
-      </c>
-      <c r="O6" t="s">
-        <v>376</v>
-      </c>
-      <c r="P6" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>506</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>418</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>441</v>
-      </c>
-      <c r="D7" s="4">
-        <v>7312</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>390</v>
-      </c>
-      <c r="F7" s="7">
-        <v>250</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="I7" s="10" t="s">
+      <c r="C41" s="5"/>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42" s="7" t="s">
         <v>448</v>
       </c>
-      <c r="J7" s="5" t="s">
-        <v>478</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="L7" s="5"/>
-      <c r="N7">
-        <v>10</v>
-      </c>
-      <c r="O7" t="s">
-        <v>376</v>
-      </c>
-      <c r="P7" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>507</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>419</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>442</v>
-      </c>
-      <c r="D8" s="4">
-        <v>7312</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>391</v>
-      </c>
-      <c r="F8" s="7">
-        <v>200</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="I8" s="11" t="s">
+      <c r="B42" s="7" t="s">
         <v>449</v>
       </c>
-      <c r="J8" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="N8">
-        <v>10</v>
-      </c>
-      <c r="O8" t="s">
-        <v>376</v>
-      </c>
-      <c r="P8" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A9" s="13" t="s">
-        <v>508</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>420</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>442</v>
-      </c>
-      <c r="D9" s="4">
-        <v>7312</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>392</v>
-      </c>
-      <c r="F9" s="7">
-        <v>200</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="I9" s="10" t="s">
+      <c r="C42" s="5"/>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43" s="7" t="s">
         <v>450</v>
       </c>
-      <c r="J9" s="4" t="s">
-        <v>480</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="N9">
-        <v>10</v>
-      </c>
-      <c r="O9" t="s">
-        <v>376</v>
-      </c>
-      <c r="P9" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>509</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>421</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>442</v>
-      </c>
-      <c r="D10" s="4">
-        <v>7312</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>393</v>
-      </c>
-      <c r="F10" s="7">
-        <v>200</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="I10" s="10" t="s">
+      <c r="B43" s="7" t="s">
         <v>451</v>
       </c>
-      <c r="J10" s="4" t="s">
-        <v>481</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="N10">
-        <v>10</v>
-      </c>
-      <c r="O10" t="s">
-        <v>376</v>
-      </c>
-      <c r="P10" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>510</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>441</v>
-      </c>
-      <c r="D11" s="4">
-        <v>7312</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>394</v>
-      </c>
-      <c r="F11" s="7">
-        <v>250</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="I11" s="10" t="s">
+      <c r="C43" s="5"/>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44" s="7" t="s">
         <v>452</v>
       </c>
-      <c r="J11" s="4" t="s">
-        <v>482</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="N11">
-        <v>10</v>
-      </c>
-      <c r="O11" t="s">
-        <v>376</v>
-      </c>
-      <c r="P11" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>511</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>423</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>441</v>
-      </c>
-      <c r="D12" s="4">
-        <v>7312</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>395</v>
-      </c>
-      <c r="F12" s="7">
-        <v>250</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="I12" s="10" t="s">
+      <c r="B44" s="7" t="s">
         <v>453</v>
       </c>
-      <c r="J12" s="4" t="s">
-        <v>483</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="N12">
-        <v>10</v>
-      </c>
-      <c r="O12" t="s">
-        <v>376</v>
-      </c>
-      <c r="P12" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A13" s="13" t="s">
-        <v>512</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>424</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>442</v>
-      </c>
-      <c r="D13" s="4">
-        <v>7312</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>396</v>
-      </c>
-      <c r="F13" s="7">
-        <v>250</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="I13" s="10" t="s">
+      <c r="C44" s="5"/>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45" s="7" t="s">
         <v>454</v>
       </c>
-      <c r="J13" s="4" t="s">
-        <v>484</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="N13">
-        <v>10</v>
-      </c>
-      <c r="O13" t="s">
-        <v>376</v>
-      </c>
-      <c r="P13" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A14" s="13" t="s">
-        <v>513</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>425</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>441</v>
-      </c>
-      <c r="D14" s="4">
-        <v>7312</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>397</v>
-      </c>
-      <c r="F14" s="7">
-        <v>250</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H14" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="I14" s="10" t="s">
+      <c r="B45" s="7" t="s">
         <v>455</v>
       </c>
-      <c r="J14" s="4" t="s">
-        <v>485</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="N14">
-        <v>10</v>
-      </c>
-      <c r="O14" t="s">
-        <v>376</v>
-      </c>
-      <c r="P14" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A15" s="13" t="s">
-        <v>514</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>426</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>441</v>
-      </c>
-      <c r="D15" s="4">
-        <v>7312</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>398</v>
-      </c>
-      <c r="F15" s="7">
-        <v>200</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H15" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="I15" s="10" t="s">
+      <c r="C45" s="5"/>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46" s="7" t="s">
         <v>456</v>
       </c>
-      <c r="J15" s="4" t="s">
-        <v>486</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="N15">
-        <v>10</v>
-      </c>
-      <c r="O15" t="s">
-        <v>376</v>
-      </c>
-      <c r="P15" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="13" t="s">
-        <v>515</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>427</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>441</v>
-      </c>
-      <c r="D16" s="4">
-        <v>7312</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>399</v>
-      </c>
-      <c r="F16" s="7">
-        <v>200</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H16" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="I16" s="10" t="s">
+      <c r="B46" s="7" t="s">
         <v>457</v>
       </c>
-      <c r="J16" s="4" t="s">
-        <v>487</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="N16">
-        <v>10</v>
-      </c>
-      <c r="O16" t="s">
-        <v>376</v>
-      </c>
-      <c r="P16" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A17" s="13" t="s">
-        <v>516</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>428</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>441</v>
-      </c>
-      <c r="D17" s="4">
-        <v>7312</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>400</v>
-      </c>
-      <c r="F17" s="7">
-        <v>200</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H17" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="I17" s="10" t="s">
-        <v>458</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>488</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="N17">
-        <v>10</v>
-      </c>
-      <c r="O17" t="s">
-        <v>376</v>
-      </c>
-      <c r="P17" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>517</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>429</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>441</v>
-      </c>
-      <c r="D18" s="4">
-        <v>7312</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>401</v>
-      </c>
-      <c r="F18" s="7">
-        <v>250</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H18" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="I18" s="10" t="s">
-        <v>459</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>489</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="N18">
-        <v>10</v>
-      </c>
-      <c r="O18" t="s">
-        <v>376</v>
-      </c>
-      <c r="P18" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A19" s="13" t="s">
-        <v>518</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>430</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>441</v>
-      </c>
-      <c r="D19" s="4">
-        <v>7312</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>402</v>
-      </c>
-      <c r="F19" s="7">
-        <v>200</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H19" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="I19" s="11" t="s">
-        <v>460</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>490</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="N19">
-        <v>10</v>
-      </c>
-      <c r="O19" t="s">
-        <v>376</v>
-      </c>
-      <c r="P19" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>519</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>431</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>441</v>
-      </c>
-      <c r="D20" s="4">
-        <v>7312</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>403</v>
-      </c>
-      <c r="F20" s="7">
-        <v>200</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H20" s="11" t="s">
-        <v>311</v>
-      </c>
-      <c r="I20" s="11" t="s">
-        <v>461</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>491</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="N20">
-        <v>10</v>
-      </c>
-      <c r="O20" t="s">
-        <v>376</v>
-      </c>
-      <c r="P20" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>520</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>432</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>441</v>
-      </c>
-      <c r="D21" s="4">
-        <v>7312</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>404</v>
-      </c>
-      <c r="F21" s="7">
-        <v>200</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H21" s="11" t="s">
-        <v>311</v>
-      </c>
-      <c r="I21" s="10" t="s">
-        <v>462</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="N21">
-        <v>10</v>
-      </c>
-      <c r="O21" t="s">
-        <v>376</v>
-      </c>
-      <c r="P21" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>521</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>433</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>442</v>
-      </c>
-      <c r="D22" s="4">
-        <v>7312</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>405</v>
-      </c>
-      <c r="F22" s="7">
-        <v>200</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H22" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="I22" s="10" t="s">
-        <v>463</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>493</v>
-      </c>
-      <c r="K22" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="N22">
-        <v>10</v>
-      </c>
-      <c r="O22" t="s">
-        <v>376</v>
-      </c>
-      <c r="P22" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>522</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>434</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>441</v>
-      </c>
-      <c r="D23" s="4">
-        <v>7312</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="F23" s="7">
-        <v>300</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H23" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="I23" s="11" t="s">
-        <v>464</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>494</v>
-      </c>
-      <c r="K23" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="N23">
-        <v>10</v>
-      </c>
-      <c r="O23" t="s">
-        <v>376</v>
-      </c>
-      <c r="P23" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>523</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>435</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>442</v>
-      </c>
-      <c r="D24" s="4">
-        <v>7312</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>407</v>
-      </c>
-      <c r="F24" s="7">
-        <v>180</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H24" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="I24" s="10" t="s">
-        <v>465</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="K24" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="N24">
-        <v>10</v>
-      </c>
-      <c r="O24" t="s">
-        <v>376</v>
-      </c>
-      <c r="P24" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>524</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>436</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>442</v>
-      </c>
-      <c r="D25" s="4">
-        <v>7312</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>408</v>
-      </c>
-      <c r="F25" s="7">
-        <v>230</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H25" s="12" t="s">
-        <v>466</v>
-      </c>
-      <c r="I25" s="10" t="s">
-        <v>467</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>496</v>
-      </c>
-      <c r="K25" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="N25">
-        <v>10</v>
-      </c>
-      <c r="O25" t="s">
-        <v>376</v>
-      </c>
-      <c r="P25" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>525</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>437</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>441</v>
-      </c>
-      <c r="D26" s="4">
-        <v>7312</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>409</v>
-      </c>
-      <c r="F26" s="7">
-        <v>250</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H26" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="I26" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>497</v>
-      </c>
-      <c r="K26" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="N26">
-        <v>10</v>
-      </c>
-      <c r="O26" t="s">
-        <v>376</v>
-      </c>
-      <c r="P26" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>526</v>
-      </c>
-      <c r="B27" s="10" t="s">
-        <v>438</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>441</v>
-      </c>
-      <c r="D27" s="4">
-        <v>7312</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>410</v>
-      </c>
-      <c r="F27" s="7">
-        <v>200</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H27" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="I27" s="10" t="s">
-        <v>469</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>498</v>
-      </c>
-      <c r="K27" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="N27">
-        <v>10</v>
-      </c>
-      <c r="O27" t="s">
-        <v>376</v>
-      </c>
-      <c r="P27" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>527</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>439</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>441</v>
-      </c>
-      <c r="D28" s="4">
-        <v>7312</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>411</v>
-      </c>
-      <c r="F28" s="7">
-        <v>200</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H28" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="I28" s="10" t="s">
-        <v>470</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>499</v>
-      </c>
-      <c r="K28" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="N28">
-        <v>10</v>
-      </c>
-      <c r="O28" t="s">
-        <v>376</v>
-      </c>
-      <c r="P28" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>528</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>440</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>441</v>
-      </c>
-      <c r="D29" s="4">
-        <v>7312</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>412</v>
-      </c>
-      <c r="F29" s="7">
-        <v>200</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H29" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="I29" s="10" t="s">
-        <v>471</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>500</v>
-      </c>
-      <c r="K29" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="N29">
-        <v>10</v>
-      </c>
-      <c r="O29" t="s">
-        <v>376</v>
-      </c>
-      <c r="P29" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A30" s="14" t="s">
-        <v>530</v>
-      </c>
-      <c r="B30" s="14" t="s">
-        <v>531</v>
-      </c>
-      <c r="C30" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>532</v>
-      </c>
-      <c r="E30" s="14" t="s">
-        <v>533</v>
-      </c>
-      <c r="F30" s="14">
-        <v>200</v>
-      </c>
-      <c r="G30" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="H30" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="I30" s="14" t="s">
-        <v>534</v>
-      </c>
-      <c r="J30" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="K30" s="14" t="s">
-        <v>536</v>
-      </c>
-      <c r="N30" s="14">
-        <v>10</v>
-      </c>
-      <c r="O30" s="14" t="s">
-        <v>376</v>
-      </c>
-      <c r="P30" s="14" t="s">
-        <v>379</v>
-      </c>
-      <c r="Q30" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="R30" s="14" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A31" s="14" t="s">
-        <v>538</v>
-      </c>
-      <c r="B31" s="14" t="s">
-        <v>539</v>
-      </c>
-      <c r="C31" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D31" s="14" t="s">
-        <v>532</v>
-      </c>
-      <c r="E31" s="14" t="s">
-        <v>540</v>
-      </c>
-      <c r="F31" s="14">
-        <v>200</v>
-      </c>
-      <c r="G31" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="H31" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="I31" s="14" t="s">
-        <v>541</v>
-      </c>
-      <c r="J31" s="14" t="s">
-        <v>542</v>
-      </c>
-      <c r="K31" s="14" t="s">
-        <v>536</v>
-      </c>
-      <c r="N31" s="14">
-        <v>10</v>
-      </c>
-      <c r="O31" s="14" t="s">
-        <v>376</v>
-      </c>
-      <c r="P31" s="14" t="s">
-        <v>379</v>
-      </c>
-      <c r="Q31" s="14" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A32" s="14" t="s">
-        <v>543</v>
-      </c>
-      <c r="B32" s="14" t="s">
-        <v>544</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>532</v>
-      </c>
-      <c r="E32" s="14" t="s">
-        <v>545</v>
-      </c>
-      <c r="F32" s="14">
-        <v>10</v>
-      </c>
-      <c r="G32" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="H32" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="I32" s="14" t="s">
-        <v>546</v>
-      </c>
-      <c r="J32" s="14" t="s">
-        <v>547</v>
-      </c>
-      <c r="K32" s="14" t="s">
-        <v>548</v>
-      </c>
-      <c r="N32" s="14">
-        <v>12.77</v>
-      </c>
-      <c r="O32" s="14" t="s">
-        <v>376</v>
-      </c>
-      <c r="P32" s="14" t="s">
-        <v>379</v>
-      </c>
-      <c r="Q32" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="R32" s="14" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A33" s="14" t="s">
-        <v>550</v>
-      </c>
-      <c r="B33" s="14" t="s">
-        <v>551</v>
-      </c>
-      <c r="C33" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D33" s="14" t="s">
-        <v>532</v>
-      </c>
-      <c r="E33" s="14" t="s">
-        <v>552</v>
-      </c>
-      <c r="F33" s="14">
-        <v>200</v>
-      </c>
-      <c r="G33" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="H33" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="I33" s="14" t="s">
-        <v>553</v>
-      </c>
-      <c r="J33" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="K33" s="14" t="s">
-        <v>536</v>
-      </c>
-      <c r="L33" s="14">
-        <v>29</v>
-      </c>
-      <c r="M33" s="14" t="s">
-        <v>376</v>
-      </c>
-      <c r="N33" s="14" t="s">
-        <v>379</v>
-      </c>
-      <c r="O33" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="P33" s="14" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A34" s="14" t="s">
-        <v>555</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>556</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D34" s="14" t="s">
-        <v>532</v>
-      </c>
-      <c r="E34" s="14" t="s">
-        <v>557</v>
-      </c>
-      <c r="F34" s="14">
-        <v>200</v>
-      </c>
-      <c r="G34" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="H34" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="I34" s="14" t="s">
-        <v>558</v>
-      </c>
-      <c r="J34" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="K34" s="14" t="s">
-        <v>536</v>
-      </c>
-      <c r="L34" s="14">
-        <v>50</v>
-      </c>
-      <c r="M34" s="14" t="s">
-        <v>376</v>
-      </c>
-      <c r="N34" s="14" t="s">
-        <v>379</v>
-      </c>
-      <c r="O34" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="P34" s="14" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A35" s="14" t="s">
-        <v>560</v>
-      </c>
-      <c r="B35" s="14" t="s">
-        <v>561</v>
-      </c>
-      <c r="C35" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D35" s="14" t="s">
-        <v>532</v>
-      </c>
-      <c r="E35" s="14" t="s">
-        <v>562</v>
-      </c>
-      <c r="F35" s="14">
-        <v>200</v>
-      </c>
-      <c r="G35" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="H35" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="I35" s="14" t="s">
-        <v>563</v>
-      </c>
-      <c r="J35" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="K35" s="14" t="s">
-        <v>536</v>
-      </c>
-      <c r="L35" s="14">
-        <v>16</v>
-      </c>
-      <c r="M35" s="14" t="s">
-        <v>376</v>
-      </c>
-      <c r="N35" s="14" t="s">
-        <v>379</v>
-      </c>
-      <c r="O35" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="P35" s="14" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A36" s="14" t="s">
-        <v>565</v>
-      </c>
-      <c r="B36" s="14" t="s">
-        <v>566</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D36" s="14" t="s">
-        <v>532</v>
-      </c>
-      <c r="E36" s="14" t="s">
-        <v>567</v>
-      </c>
-      <c r="F36" s="14">
-        <v>100</v>
-      </c>
-      <c r="G36" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="H36" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="I36" s="14" t="s">
-        <v>568</v>
-      </c>
-      <c r="J36" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="K36" s="14" t="s">
-        <v>536</v>
-      </c>
-      <c r="L36" s="14">
-        <v>0.10661</v>
-      </c>
-      <c r="M36" s="14" t="s">
-        <v>375</v>
-      </c>
-      <c r="N36" s="14" t="s">
-        <v>379</v>
-      </c>
-      <c r="O36" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="P36" s="14" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A37" s="14" t="s">
-        <v>570</v>
-      </c>
-      <c r="B37" s="14" t="s">
-        <v>571</v>
-      </c>
-      <c r="C37" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D37" s="14" t="s">
-        <v>532</v>
-      </c>
-      <c r="E37" s="14" t="s">
-        <v>572</v>
-      </c>
-      <c r="F37" s="14">
-        <v>200</v>
-      </c>
-      <c r="G37" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="H37" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="I37" s="14" t="s">
-        <v>573</v>
-      </c>
-      <c r="J37" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="K37" s="14" t="s">
-        <v>536</v>
-      </c>
-      <c r="L37" s="14">
-        <v>5.5555555555555601E-2</v>
-      </c>
-      <c r="M37" s="14" t="s">
-        <v>375</v>
-      </c>
-      <c r="N37" s="14" t="s">
-        <v>379</v>
-      </c>
-      <c r="O37" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="P37" s="14" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A38" s="14" t="s">
-        <v>575</v>
-      </c>
-      <c r="B38" s="14" t="s">
-        <v>576</v>
-      </c>
-      <c r="C38" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D38" s="14" t="s">
-        <v>532</v>
-      </c>
-      <c r="E38" s="14" t="s">
-        <v>577</v>
-      </c>
-      <c r="F38" s="14">
-        <v>100</v>
-      </c>
-      <c r="G38" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="H38" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="I38" s="14" t="s">
-        <v>578</v>
-      </c>
-      <c r="J38" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="K38" s="14" t="s">
-        <v>536</v>
-      </c>
-      <c r="L38" s="14">
-        <v>0.11279043537108099</v>
-      </c>
-      <c r="M38" s="14" t="s">
-        <v>375</v>
-      </c>
-      <c r="N38" s="14" t="s">
-        <v>379</v>
-      </c>
-      <c r="O38" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="P38" s="14" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A39" s="14" t="s">
-        <v>579</v>
-      </c>
-      <c r="B39" s="14" t="s">
-        <v>580</v>
-      </c>
-      <c r="C39" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D39" s="14" t="s">
-        <v>532</v>
-      </c>
-      <c r="E39" s="14" t="s">
-        <v>581</v>
-      </c>
-      <c r="F39" s="14">
-        <v>1.3</v>
-      </c>
-      <c r="G39" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="H39" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="I39" s="14" t="s">
-        <v>582</v>
-      </c>
-      <c r="J39" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="K39" s="14" t="s">
-        <v>536</v>
-      </c>
-      <c r="L39" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="M39" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="N39" s="14" t="s">
-        <v>379</v>
-      </c>
-      <c r="O39" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="P39" s="14" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A40" s="14" t="s">
-        <v>583</v>
-      </c>
-      <c r="B40" s="14" t="s">
-        <v>556</v>
-      </c>
-      <c r="C40" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D40" s="14" t="s">
-        <v>532</v>
-      </c>
-      <c r="E40" s="14" t="s">
-        <v>584</v>
-      </c>
-      <c r="F40" s="14">
-        <v>1.49</v>
-      </c>
-      <c r="G40" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="H40" s="14" t="s">
-        <v>585</v>
-      </c>
-      <c r="I40" s="14" t="s">
-        <v>586</v>
-      </c>
-      <c r="J40" s="14" t="s">
-        <v>585</v>
-      </c>
-      <c r="K40" s="14" t="s">
-        <v>536</v>
-      </c>
-      <c r="L40" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="M40" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="N40" s="14" t="s">
-        <v>379</v>
-      </c>
-      <c r="O40" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="P40" s="14" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A41" s="14" t="s">
-        <v>587</v>
-      </c>
-      <c r="B41" s="14" t="s">
-        <v>588</v>
-      </c>
-      <c r="C41" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D41" s="14" t="s">
-        <v>532</v>
-      </c>
-      <c r="E41" s="14" t="s">
-        <v>589</v>
-      </c>
-      <c r="F41" s="14">
-        <v>17.23</v>
-      </c>
-      <c r="G41" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="H41" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="I41" s="14" t="s">
-        <v>590</v>
-      </c>
-      <c r="J41" s="14" t="s">
-        <v>591</v>
-      </c>
-      <c r="K41" s="14" t="s">
-        <v>536</v>
-      </c>
-      <c r="L41" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="M41" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="N41" s="14" t="s">
-        <v>379</v>
-      </c>
-      <c r="O41" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="P41" s="14" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A42" s="14" t="s">
-        <v>592</v>
-      </c>
-      <c r="B42" s="14" t="s">
-        <v>593</v>
-      </c>
-      <c r="C42" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D42" s="14" t="s">
-        <v>532</v>
-      </c>
-      <c r="E42" s="14" t="s">
-        <v>594</v>
-      </c>
-      <c r="F42" s="14">
-        <v>200</v>
-      </c>
-      <c r="G42" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="H42" s="14" t="s">
-        <v>365</v>
-      </c>
-      <c r="I42" s="14" t="s">
-        <v>595</v>
-      </c>
-      <c r="J42" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="K42" s="14" t="s">
-        <v>536</v>
-      </c>
-      <c r="L42" s="14">
-        <v>77</v>
-      </c>
-      <c r="M42" s="14" t="s">
-        <v>376</v>
-      </c>
-      <c r="N42" s="14" t="s">
-        <v>379</v>
-      </c>
-      <c r="O42" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="P42" s="14" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A43" s="14" t="s">
-        <v>596</v>
-      </c>
-      <c r="B43" s="14" t="s">
-        <v>597</v>
-      </c>
-      <c r="C43" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D43" s="14" t="s">
-        <v>532</v>
-      </c>
-      <c r="E43" s="14" t="s">
-        <v>598</v>
-      </c>
-      <c r="F43" s="14">
-        <v>200</v>
-      </c>
-      <c r="G43" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="H43" s="14" t="s">
-        <v>365</v>
-      </c>
-      <c r="I43" s="14" t="s">
-        <v>599</v>
-      </c>
-      <c r="J43" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="K43" s="14" t="s">
-        <v>536</v>
-      </c>
-      <c r="L43" s="14">
-        <v>77</v>
-      </c>
-      <c r="M43" s="14" t="s">
-        <v>376</v>
-      </c>
-      <c r="N43" s="14" t="s">
-        <v>379</v>
-      </c>
-      <c r="O43" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="P43" s="14" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A44" s="14" t="s">
-        <v>600</v>
-      </c>
-      <c r="B44" s="14" t="s">
-        <v>601</v>
-      </c>
-      <c r="C44" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D44" s="14" t="s">
-        <v>532</v>
-      </c>
-      <c r="E44" s="14" t="s">
-        <v>602</v>
-      </c>
-      <c r="F44" s="14">
-        <v>200</v>
-      </c>
-      <c r="G44" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="H44" s="14" t="s">
-        <v>365</v>
-      </c>
-      <c r="I44" s="14" t="s">
-        <v>603</v>
-      </c>
-      <c r="J44" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="K44" s="14" t="s">
-        <v>536</v>
-      </c>
-      <c r="L44" s="14">
-        <v>73</v>
-      </c>
-      <c r="M44" s="14" t="s">
-        <v>376</v>
-      </c>
-      <c r="N44" s="14" t="s">
-        <v>379</v>
-      </c>
-      <c r="O44" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="P44" s="14" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A45" s="14" t="s">
-        <v>604</v>
-      </c>
-      <c r="B45" s="14" t="s">
-        <v>605</v>
-      </c>
-      <c r="C45" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D45" s="14" t="s">
-        <v>532</v>
-      </c>
-      <c r="E45" s="14" t="s">
-        <v>606</v>
-      </c>
-      <c r="F45" s="14">
-        <v>200</v>
-      </c>
-      <c r="G45" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="H45" s="14" t="s">
-        <v>365</v>
-      </c>
-      <c r="I45" s="14" t="s">
-        <v>607</v>
-      </c>
-      <c r="J45" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="K45" s="14" t="s">
-        <v>536</v>
-      </c>
-      <c r="L45" s="14">
-        <v>70</v>
-      </c>
-      <c r="M45" s="14" t="s">
-        <v>376</v>
-      </c>
-      <c r="N45" s="14" t="s">
-        <v>379</v>
-      </c>
-      <c r="O45" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="P45" s="14" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A46" s="14" t="s">
-        <v>608</v>
-      </c>
-      <c r="B46" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="C46" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D46" s="14" t="s">
-        <v>532</v>
-      </c>
-      <c r="E46" s="14" t="s">
-        <v>610</v>
-      </c>
-      <c r="F46" s="14">
-        <v>200</v>
-      </c>
-      <c r="G46" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="H46" s="14" t="s">
-        <v>365</v>
-      </c>
-      <c r="I46" s="14" t="s">
-        <v>611</v>
-      </c>
-      <c r="J46" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="K46" s="14" t="s">
-        <v>536</v>
-      </c>
-      <c r="L46" s="14">
-        <v>70</v>
-      </c>
-      <c r="M46" s="14" t="s">
-        <v>376</v>
-      </c>
-      <c r="N46" s="14" t="s">
-        <v>379</v>
-      </c>
-      <c r="O46" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="P46" s="14" t="s">
-        <v>535</v>
-      </c>
+      <c r="C46" s="5"/>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47" s="5"/>
+      <c r="B47" s="8"/>
+      <c r="C47" s="5"/>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48" s="5"/>
+      <c r="B48" s="8"/>
+      <c r="C48" s="5"/>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49" s="5"/>
+      <c r="B49" s="8"/>
+      <c r="C49" s="5"/>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50" s="5"/>
+      <c r="B50" s="8"/>
+      <c r="C50" s="5"/>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51" s="5"/>
+      <c r="B51" s="8"/>
+      <c r="C51" s="5"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52" s="5"/>
+      <c r="B52" s="8"/>
+      <c r="C52" s="5"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53" s="5"/>
+      <c r="B53" s="8"/>
+      <c r="C53" s="5"/>
     </row>
   </sheetData>
-  <dataValidations count="5">
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please enter a number/decimal" sqref="F2:F1001" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>0</formula1>
-      <formula2>1000000</formula2>
-    </dataValidation>
+  <dataValidations count="1">
     <dataValidation type="textLength" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please enter a structure" sqref="B2:B1001" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>1</formula1>
-    </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{00000000-0002-0000-0000-000003000000}">
-      <formula1>2001</formula1>
-      <formula2>9999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Project code required" error="Please enter the 4 digit project code" sqref="D2:D1048576" xr:uid="{00000000-0002-0000-0000-000004000000}">
-      <formula1>2001</formula1>
-      <formula2>9999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please enter a decimal greater than 0" sqref="N2:N29 P30:P32 N33:N1001" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>0</formula1>
-      <formula2>100</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please choose from the list" xr:uid="{00000000-0002-0000-0000-000005000000}">
-          <x14:formula1>
-            <xm:f>Dropdowns!$A$1:$A$11</xm:f>
-          </x14:formula1>
-          <xm:sqref>C2:C1001</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please choose units from the list" xr:uid="{00000000-0002-0000-0000-000006000000}">
-          <x14:formula1>
-            <xm:f>Dropdowns!$B$1:$B$7</xm:f>
-          </x14:formula1>
-          <xm:sqref>G2:G1001</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please choose from the supplier list" xr:uid="{00000000-0002-0000-0000-000007000000}">
-          <x14:formula1>
-            <xm:f>Dropdowns!$C$1:$C$344</xm:f>
-          </x14:formula1>
-          <xm:sqref>H2:H1001</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000008000000}">
-          <x14:formula1>
-            <xm:f>Dropdowns!$D$1:$D$4</xm:f>
-          </x14:formula1>
-          <xm:sqref>O2:O29 Q30:Q32 O33:O1001</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000009000000}">
-          <x14:formula1>
-            <xm:f>Dropdowns!$E$1</xm:f>
-          </x14:formula1>
-          <xm:sqref>P2:P29 P33:P1001 J31 R30 R32</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000A000000}">
-          <x14:formula1>
-            <xm:f>Dropdowns!$F$1:$F$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>R2:R30 R32:R1048576 J31</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
@@ -4526,19 +2260,19 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="E1" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="F1">
         <v>96</v>
@@ -4546,16 +2280,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="F2">
         <v>384</v>
@@ -4563,16 +2297,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="F3">
         <v>1536</v>
@@ -4580,1746 +2314,1746 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>378</v>
+        <v>365</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
         <v>17</v>
       </c>
-      <c r="B5" t="s">
-        <v>30</v>
-      </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C12" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C13" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C14" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C15" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C16" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C17" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C18" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C19" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C20" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C21" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C22" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C23" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C24" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C25" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C26" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C27" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C28" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C29" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C30" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C31" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C32" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C33" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C34" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
     </row>
     <row r="35" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C35" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="36" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C36" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="37" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C37" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
     </row>
     <row r="38" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C38" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
     </row>
     <row r="39" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C39" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
     </row>
     <row r="40" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C40" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
     </row>
     <row r="41" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C41" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
     </row>
     <row r="42" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C42" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
     </row>
     <row r="43" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C43" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
     </row>
     <row r="44" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C44" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
     </row>
     <row r="45" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C45" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
     </row>
     <row r="46" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C46" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
     </row>
     <row r="47" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C47" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
     </row>
     <row r="48" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C48" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
     </row>
     <row r="49" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C49" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
     </row>
     <row r="50" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C50" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
     </row>
     <row r="51" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C51" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
     </row>
     <row r="52" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C52" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
     </row>
     <row r="53" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C53" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
     </row>
     <row r="54" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C54" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
     </row>
     <row r="55" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C55" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
     </row>
     <row r="56" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C56" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
     </row>
     <row r="57" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C57" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
     </row>
     <row r="58" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C58" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
     </row>
     <row r="59" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C59" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
     </row>
     <row r="60" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C60" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
     </row>
     <row r="61" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C61" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
     </row>
     <row r="62" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C62" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
     </row>
     <row r="63" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C63" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
     </row>
     <row r="64" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C64" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
     </row>
     <row r="65" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C65" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
     </row>
     <row r="66" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C66" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
     </row>
     <row r="67" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C67" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
     </row>
     <row r="68" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C68" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
     </row>
     <row r="69" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C69" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
     </row>
     <row r="70" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C70" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
     </row>
     <row r="71" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C71" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
     </row>
     <row r="72" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C72" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
     </row>
     <row r="73" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C73" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
     </row>
     <row r="74" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C74" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
     </row>
     <row r="75" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C75" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
     </row>
     <row r="76" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C76" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
     </row>
     <row r="77" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C77" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="78" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C78" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
     </row>
     <row r="79" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C79" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
     </row>
     <row r="80" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C80" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
     </row>
     <row r="81" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C81" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
     </row>
     <row r="82" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C82" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
     </row>
     <row r="83" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C83" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
     </row>
     <row r="84" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C84" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
     </row>
     <row r="85" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C85" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
     </row>
     <row r="86" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C86" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
     </row>
     <row r="87" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C87" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
     </row>
     <row r="88" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C88" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
     </row>
     <row r="89" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C89" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
     </row>
     <row r="90" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C90" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
     </row>
     <row r="91" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C91" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
     </row>
     <row r="92" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C92" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
     </row>
     <row r="93" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C93" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
     </row>
     <row r="94" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C94" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
     </row>
     <row r="95" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C95" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
     </row>
     <row r="96" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C96" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
     </row>
     <row r="97" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C97" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
     </row>
     <row r="98" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C98" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
     </row>
     <row r="99" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C99" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
     </row>
     <row r="100" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C100" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
     </row>
     <row r="101" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C101" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
     </row>
     <row r="102" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C102" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
     </row>
     <row r="103" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C103" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
     </row>
     <row r="104" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C104" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
     </row>
     <row r="105" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C105" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
     </row>
     <row r="106" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C106" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
     </row>
     <row r="107" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C107" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
     </row>
     <row r="108" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C108" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
     </row>
     <row r="109" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C109" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
     </row>
     <row r="110" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C110" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
     </row>
     <row r="111" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C111" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
     </row>
     <row r="112" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C112" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
     </row>
     <row r="113" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C113" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
     </row>
     <row r="114" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C114" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
     </row>
     <row r="115" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C115" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
     </row>
     <row r="116" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C116" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="117" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C117" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
     </row>
     <row r="118" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C118" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="119" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C119" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
     </row>
     <row r="120" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C120" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
     </row>
     <row r="121" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C121" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
     </row>
     <row r="122" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C122" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
     </row>
     <row r="123" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C123" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
     </row>
     <row r="124" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C124" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
     </row>
     <row r="125" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C125" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
     </row>
     <row r="126" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C126" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="127" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C127" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
     </row>
     <row r="128" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C128" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
     </row>
     <row r="129" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C129" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
     </row>
     <row r="130" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C130" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
     </row>
     <row r="131" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C131" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
     </row>
     <row r="132" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C132" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
     </row>
     <row r="133" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C133" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="134" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C134" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
     </row>
     <row r="135" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C135" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
     </row>
     <row r="136" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C136" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
     </row>
     <row r="137" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C137" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
     </row>
     <row r="138" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C138" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
     </row>
     <row r="139" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C139" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
     </row>
     <row r="140" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C140" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
     </row>
     <row r="141" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C141" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
     </row>
     <row r="142" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C142" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
     </row>
     <row r="143" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C143" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
     </row>
     <row r="144" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C144" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
     </row>
     <row r="145" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C145" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
     </row>
     <row r="146" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C146" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
     </row>
     <row r="147" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C147" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
     </row>
     <row r="148" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C148" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
     </row>
     <row r="149" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C149" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
     </row>
     <row r="150" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C150" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
     </row>
     <row r="151" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C151" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
     </row>
     <row r="152" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C152" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
     </row>
     <row r="153" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C153" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
     </row>
     <row r="154" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C154" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
     </row>
     <row r="155" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C155" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
     </row>
     <row r="156" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C156" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
     </row>
     <row r="157" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C157" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
     </row>
     <row r="158" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C158" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
     </row>
     <row r="159" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C159" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
     </row>
     <row r="160" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C160" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
     </row>
     <row r="161" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C161" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
     </row>
     <row r="162" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C162" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
     </row>
     <row r="163" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C163" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
     </row>
     <row r="164" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C164" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
     </row>
     <row r="165" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C165" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
     </row>
     <row r="166" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C166" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
     </row>
     <row r="167" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C167" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
     </row>
     <row r="168" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C168" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
     </row>
     <row r="169" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C169" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
     </row>
     <row r="170" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C170" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
     </row>
     <row r="171" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C171" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
     </row>
     <row r="172" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C172" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
     </row>
     <row r="173" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C173" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
     </row>
     <row r="174" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C174" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
     </row>
     <row r="175" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C175" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="176" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C176" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="177" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C177" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
     </row>
     <row r="178" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C178" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
     </row>
     <row r="179" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C179" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
     </row>
     <row r="180" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C180" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
     </row>
     <row r="181" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C181" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
     </row>
     <row r="182" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C182" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
     </row>
     <row r="183" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C183" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
     </row>
     <row r="184" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C184" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
     </row>
     <row r="185" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C185" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
     </row>
     <row r="186" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C186" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
     </row>
     <row r="187" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C187" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
     </row>
     <row r="188" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C188" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
     </row>
     <row r="189" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C189" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
     </row>
     <row r="190" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C190" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
     </row>
     <row r="191" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C191" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
     </row>
     <row r="192" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C192" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
     </row>
     <row r="193" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C193" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
     </row>
     <row r="194" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C194" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
     </row>
     <row r="195" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C195" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
     </row>
     <row r="196" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C196" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
     </row>
     <row r="197" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C197" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
     </row>
     <row r="198" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C198" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
     </row>
     <row r="199" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C199" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
     </row>
     <row r="200" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C200" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
     </row>
     <row r="201" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C201" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
     </row>
     <row r="202" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C202" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
     </row>
     <row r="203" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C203" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
     </row>
     <row r="204" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C204" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
     </row>
     <row r="205" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C205" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
     </row>
     <row r="206" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C206" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
     </row>
     <row r="207" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C207" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
     </row>
     <row r="208" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C208" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
     </row>
     <row r="209" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C209" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
     </row>
     <row r="210" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C210" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
     </row>
     <row r="211" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C211" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
     </row>
     <row r="212" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C212" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
     </row>
     <row r="213" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C213" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
     </row>
     <row r="214" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C214" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
     </row>
     <row r="215" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C215" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
     </row>
     <row r="216" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C216" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
     </row>
     <row r="217" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C217" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
     </row>
     <row r="218" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C218" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
     </row>
     <row r="219" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C219" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
     </row>
     <row r="220" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C220" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
     </row>
     <row r="221" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C221" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
     </row>
     <row r="222" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C222" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
     </row>
     <row r="223" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C223" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
     </row>
     <row r="224" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C224" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
     </row>
     <row r="225" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C225" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
     </row>
     <row r="226" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C226" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
     </row>
     <row r="227" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C227" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
     </row>
     <row r="228" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C228" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
     </row>
     <row r="229" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C229" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
     </row>
     <row r="230" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C230" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
     </row>
     <row r="231" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C231" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
     </row>
     <row r="232" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C232" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
     </row>
     <row r="233" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C233" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
     </row>
     <row r="234" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C234" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
     </row>
     <row r="235" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C235" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
     </row>
     <row r="236" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C236" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
     </row>
     <row r="237" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C237" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
     </row>
     <row r="238" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C238" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
     </row>
     <row r="239" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C239" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
     </row>
     <row r="240" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C240" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
     </row>
     <row r="241" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C241" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
     </row>
     <row r="242" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C242" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
     </row>
     <row r="243" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C243" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
     </row>
     <row r="244" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C244" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
     </row>
     <row r="245" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C245" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
     </row>
     <row r="246" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C246" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
     </row>
     <row r="247" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C247" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
     </row>
     <row r="248" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C248" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
     </row>
     <row r="249" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C249" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
     </row>
     <row r="250" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C250" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
     </row>
     <row r="251" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C251" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
     </row>
     <row r="252" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C252" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
     </row>
     <row r="253" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C253" t="s">
-        <v>283</v>
+        <v>270</v>
       </c>
     </row>
     <row r="254" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C254" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
     </row>
     <row r="255" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C255" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
     </row>
     <row r="256" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C256" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
     </row>
     <row r="257" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C257" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
     </row>
     <row r="258" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C258" t="s">
-        <v>288</v>
+        <v>275</v>
       </c>
     </row>
     <row r="259" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C259" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
     </row>
     <row r="260" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C260" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
     </row>
     <row r="261" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C261" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
     </row>
     <row r="262" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C262" t="s">
-        <v>292</v>
+        <v>279</v>
       </c>
     </row>
     <row r="263" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C263" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
     </row>
     <row r="264" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C264" t="s">
-        <v>294</v>
+        <v>281</v>
       </c>
     </row>
     <row r="265" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C265" t="s">
-        <v>295</v>
+        <v>282</v>
       </c>
     </row>
     <row r="266" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C266" t="s">
-        <v>296</v>
+        <v>283</v>
       </c>
     </row>
     <row r="267" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C267" t="s">
-        <v>297</v>
+        <v>284</v>
       </c>
     </row>
     <row r="268" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C268" t="s">
-        <v>298</v>
+        <v>285</v>
       </c>
     </row>
     <row r="269" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C269" t="s">
-        <v>299</v>
+        <v>286</v>
       </c>
     </row>
     <row r="270" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C270" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
     </row>
     <row r="271" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C271" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
     </row>
     <row r="272" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C272" t="s">
-        <v>302</v>
+        <v>289</v>
       </c>
     </row>
     <row r="273" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C273" t="s">
-        <v>303</v>
+        <v>290</v>
       </c>
     </row>
     <row r="274" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C274" t="s">
-        <v>304</v>
+        <v>291</v>
       </c>
     </row>
     <row r="275" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C275" t="s">
-        <v>305</v>
+        <v>292</v>
       </c>
     </row>
     <row r="276" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C276" t="s">
-        <v>306</v>
+        <v>293</v>
       </c>
     </row>
     <row r="277" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C277" t="s">
-        <v>307</v>
+        <v>294</v>
       </c>
     </row>
     <row r="278" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C278" t="s">
-        <v>308</v>
+        <v>295</v>
       </c>
     </row>
     <row r="279" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C279" t="s">
-        <v>309</v>
+        <v>296</v>
       </c>
     </row>
     <row r="280" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C280" t="s">
-        <v>310</v>
+        <v>297</v>
       </c>
     </row>
     <row r="281" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C281" t="s">
-        <v>311</v>
+        <v>298</v>
       </c>
     </row>
     <row r="282" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C282" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
     </row>
     <row r="283" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C283" t="s">
-        <v>313</v>
+        <v>300</v>
       </c>
     </row>
     <row r="284" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C284" t="s">
-        <v>314</v>
+        <v>301</v>
       </c>
     </row>
     <row r="285" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C285" t="s">
-        <v>315</v>
+        <v>302</v>
       </c>
     </row>
     <row r="286" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C286" t="s">
-        <v>316</v>
+        <v>303</v>
       </c>
     </row>
     <row r="287" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C287" t="s">
-        <v>317</v>
+        <v>304</v>
       </c>
     </row>
     <row r="288" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C288" t="s">
-        <v>318</v>
+        <v>305</v>
       </c>
     </row>
     <row r="289" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C289" t="s">
-        <v>319</v>
+        <v>306</v>
       </c>
     </row>
     <row r="290" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C290" t="s">
-        <v>320</v>
+        <v>307</v>
       </c>
     </row>
     <row r="291" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C291" t="s">
-        <v>321</v>
+        <v>308</v>
       </c>
     </row>
     <row r="292" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C292" t="s">
-        <v>322</v>
+        <v>309</v>
       </c>
     </row>
     <row r="293" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C293" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
     </row>
     <row r="294" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C294" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
     </row>
     <row r="295" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C295" t="s">
-        <v>325</v>
+        <v>312</v>
       </c>
     </row>
     <row r="296" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C296" t="s">
-        <v>326</v>
+        <v>313</v>
       </c>
     </row>
     <row r="297" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C297" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
     </row>
     <row r="298" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C298" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
     </row>
     <row r="299" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C299" t="s">
-        <v>329</v>
+        <v>316</v>
       </c>
     </row>
     <row r="300" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C300" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
     </row>
     <row r="301" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C301" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
     </row>
     <row r="302" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C302" t="s">
-        <v>332</v>
+        <v>319</v>
       </c>
     </row>
     <row r="303" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C303" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
     </row>
     <row r="304" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C304" t="s">
-        <v>334</v>
+        <v>321</v>
       </c>
     </row>
     <row r="305" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C305" t="s">
-        <v>335</v>
+        <v>322</v>
       </c>
     </row>
     <row r="306" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C306" t="s">
-        <v>336</v>
+        <v>323</v>
       </c>
     </row>
     <row r="307" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C307" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
     </row>
     <row r="308" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C308" t="s">
-        <v>338</v>
+        <v>325</v>
       </c>
     </row>
     <row r="309" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C309" t="s">
-        <v>339</v>
+        <v>326</v>
       </c>
     </row>
     <row r="310" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C310" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
     </row>
     <row r="311" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C311" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
     </row>
     <row r="312" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C312" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
     </row>
     <row r="313" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C313" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
     </row>
     <row r="314" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C314" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
     </row>
     <row r="315" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C315" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
     </row>
     <row r="316" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C316" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
     </row>
     <row r="317" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C317" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
     </row>
     <row r="318" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C318" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
     </row>
     <row r="319" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C319" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
     </row>
     <row r="320" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C320" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
     </row>
     <row r="321" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C321" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
     </row>
     <row r="322" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C322" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
     </row>
     <row r="323" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C323" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
     </row>
     <row r="324" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C324" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
     </row>
     <row r="325" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C325" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
     </row>
     <row r="326" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C326" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
     </row>
     <row r="327" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C327" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
     </row>
     <row r="328" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C328" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
     </row>
     <row r="329" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C329" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
     </row>
     <row r="330" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C330" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
     </row>
     <row r="331" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C331" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
     </row>
     <row r="332" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C332" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
     </row>
     <row r="333" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C333" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
     </row>
     <row r="334" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C334" t="s">
-        <v>364</v>
+        <v>351</v>
       </c>
     </row>
     <row r="335" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C335" t="s">
-        <v>365</v>
+        <v>352</v>
       </c>
     </row>
     <row r="336" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C336" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
     </row>
     <row r="337" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C337" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
     </row>
     <row r="338" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C338" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
     </row>
     <row r="339" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C339" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
     </row>
     <row r="340" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C340" t="s">
-        <v>370</v>
+        <v>357</v>
       </c>
     </row>
     <row r="341" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C341" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
     </row>
     <row r="342" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C342" t="s">
-        <v>372</v>
+        <v>359</v>
       </c>
     </row>
     <row r="343" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C343" t="s">
-        <v>373</v>
+        <v>360</v>
       </c>
     </row>
     <row r="344" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C344" t="s">
-        <v>374</v>
+        <v>361</v>
       </c>
     </row>
   </sheetData>
